--- a/data_src/xlsx表/投稿模板表.xlsx
+++ b/data_src/xlsx表/投稿模板表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,6 +707,1068 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4" t="n">
+        <v>903</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>清晰侧脸路透</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>今天一号航站楼出口蹲到的，画质能看清穿搭，先马住。</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>240</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101</v>
+      </c>
+      <c r="C5" t="n">
+        <v>903</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>远距离跟拍</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>人太多了只拍到背影，但确认是今天那班。</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>360</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101</v>
+      </c>
+      <c r="C6" t="n">
+        <v>903</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>糊图也发</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>手抖了将就看看，至少证明真的到了。</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>480</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102</v>
+      </c>
+      <c r="C7" t="n">
+        <v>903</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>行李车近景</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>推着行李车出来的瞬间抓到了，侧脸线条很清楚。</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>240</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>20</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102</v>
+      </c>
+      <c r="C8" t="n">
+        <v>903</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>保镖挡镜头</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>安保围得严，只漏出半个帽檐，凑合存。</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>360</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102</v>
+      </c>
+      <c r="C9" t="n">
+        <v>903</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>接机口远照</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>站在栏杆外拍的，小但能对上时间。</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>480</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103</v>
+      </c>
+      <c r="C10" t="n">
+        <v>903</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>会员线人近景</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>线人反馈的近距离图，五官和外套都能对上。</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>240</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="n">
+        <v>103</v>
+      </c>
+      <c r="C11" t="n">
+        <v>903</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>贵宾通道出口</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>走的贵宾通道，拍到上车前最后一眼。</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>360</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="n">
+        <v>103</v>
+      </c>
+      <c r="C12" t="n">
+        <v>903</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>停车场抓拍</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>上车前在停车场停了一秒，刚好按到快门。</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>480</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="n">
+        <v>201</v>
+      </c>
+      <c r="C13" t="n">
+        <v>903</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>拼盘现场前排</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>开场曲第一句就炸了，这位置值回票价。</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>360</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>20</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="n">
+        <v>201</v>
+      </c>
+      <c r="C14" t="n">
+        <v>903</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" t="n">
+        <v>40</v>
+      </c>
+      <c r="H14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>看台中层视角</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>中层也能看清舞台，灯光打下来全场都在喊。</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>480</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>12</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="n">
+        <v>201</v>
+      </c>
+      <c r="C15" t="n">
+        <v>903</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>末排听响repo</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>离得远但氛围拉满，录了一段现场音。</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>720</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="n">
+        <v>202</v>
+      </c>
+      <c r="C16" t="n">
+        <v>903</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>第二现场前排</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>第二段出场的时候全场手机灯海，前排视野无敌。</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>360</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>20</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="n">
+        <v>202</v>
+      </c>
+      <c r="C17" t="n">
+        <v>903</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" t="n">
+        <v>40</v>
+      </c>
+      <c r="H17" t="n">
+        <v>25</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>侧台视角</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>侧面能看到候场动静，演出节奏比想象中快。</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>480</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>12</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="n">
+        <v>202</v>
+      </c>
+      <c r="C18" t="n">
+        <v>903</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>散场人流</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>散场人挤人，只拍到背影和应援色。</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>720</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="n">
+        <v>203</v>
+      </c>
+      <c r="C19" t="n">
+        <v>903</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>内场前排repo</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>内场前排看到的表情细节，这次真的离很近。</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>360</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="n">
+        <v>203</v>
+      </c>
+      <c r="C20" t="n">
+        <v>903</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" t="n">
+        <v>25</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>后台口偶遇</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>散场后在后台口等到片刻，拍到上车前挥手。</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>480</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>14</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="n">
+        <v>203</v>
+      </c>
+      <c r="C21" t="n">
+        <v>903</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>工作人员通道</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>工作人员通道边远远拍到一组，算意外收获。</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>720</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_src/xlsx表/投稿模板表.xlsx
+++ b/data_src/xlsx表/投稿模板表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1769,6 +1769,71 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>9001</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>101</v>
+      </c>
+      <c r="C22" t="n">
+        <v>903</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>tutorial_seed</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>教程嫂子路透</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>新手引导预置帖，曝光秒结算。</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_src/xlsx表/投稿模板表.xlsx
+++ b/data_src/xlsx表/投稿模板表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,6 @@
       <c r="H4" t="n">
         <v>50</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>清晰侧脸路透</t>
@@ -745,8 +744,6 @@
           <t>今天一号航站楼出口蹲到的，画质能看清穿搭，先马住。</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>240</v>
       </c>
@@ -793,7 +790,6 @@
       <c r="H5" t="n">
         <v>25</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>远距离跟拍</t>
@@ -804,8 +800,6 @@
           <t>人太多了只拍到背影，但确认是今天那班。</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>360</v>
       </c>
@@ -852,7 +846,6 @@
       <c r="H6" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>糊图也发</t>
@@ -863,8 +856,6 @@
           <t>手抖了将就看看，至少证明真的到了。</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>480</v>
       </c>
@@ -911,7 +902,6 @@
       <c r="H7" t="n">
         <v>50</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>行李车近景</t>
@@ -922,8 +912,6 @@
           <t>推着行李车出来的瞬间抓到了，侧脸线条很清楚。</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>240</v>
       </c>
@@ -970,7 +958,6 @@
       <c r="H8" t="n">
         <v>25</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>保镖挡镜头</t>
@@ -981,8 +968,6 @@
           <t>安保围得严，只漏出半个帽檐，凑合存。</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
         <v>360</v>
       </c>
@@ -1029,7 +1014,6 @@
       <c r="H9" t="n">
         <v>10</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>接机口远照</t>
@@ -1040,8 +1024,6 @@
           <t>站在栏杆外拍的，小但能对上时间。</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>480</v>
       </c>
@@ -1088,7 +1070,6 @@
       <c r="H10" t="n">
         <v>50</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>会员线人近景</t>
@@ -1099,8 +1080,6 @@
           <t>线人反馈的近距离图，五官和外套都能对上。</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>240</v>
       </c>
@@ -1147,7 +1126,6 @@
       <c r="H11" t="n">
         <v>25</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>贵宾通道出口</t>
@@ -1158,8 +1136,6 @@
           <t>走的贵宾通道，拍到上车前最后一眼。</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>360</v>
       </c>
@@ -1206,7 +1182,6 @@
       <c r="H12" t="n">
         <v>10</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>停车场抓拍</t>
@@ -1217,8 +1192,6 @@
           <t>上车前在停车场停了一秒，刚好按到快门。</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>480</v>
       </c>
@@ -1265,7 +1238,6 @@
       <c r="H13" t="n">
         <v>50</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>拼盘现场前排</t>
@@ -1276,8 +1248,6 @@
           <t>开场曲第一句就炸了，这位置值回票价。</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>360</v>
       </c>
@@ -1324,7 +1294,6 @@
       <c r="H14" t="n">
         <v>25</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>看台中层视角</t>
@@ -1335,8 +1304,6 @@
           <t>中层也能看清舞台，灯光打下来全场都在喊。</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>480</v>
       </c>
@@ -1383,7 +1350,6 @@
       <c r="H15" t="n">
         <v>10</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>末排听响repo</t>
@@ -1394,8 +1360,6 @@
           <t>离得远但氛围拉满，录了一段现场音。</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>720</v>
       </c>
@@ -1442,7 +1406,6 @@
       <c r="H16" t="n">
         <v>50</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>第二现场前排</t>
@@ -1453,8 +1416,6 @@
           <t>第二段出场的时候全场手机灯海，前排视野无敌。</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>360</v>
       </c>
@@ -1501,7 +1462,6 @@
       <c r="H17" t="n">
         <v>25</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>侧台视角</t>
@@ -1512,8 +1472,6 @@
           <t>侧面能看到候场动静，演出节奏比想象中快。</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
         <v>480</v>
       </c>
@@ -1560,7 +1518,6 @@
       <c r="H18" t="n">
         <v>10</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>散场人流</t>
@@ -1571,8 +1528,6 @@
           <t>散场人挤人，只拍到背影和应援色。</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>720</v>
       </c>
@@ -1619,7 +1574,6 @@
       <c r="H19" t="n">
         <v>50</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>内场前排repo</t>
@@ -1630,8 +1584,6 @@
           <t>内场前排看到的表情细节，这次真的离很近。</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>360</v>
       </c>
@@ -1678,7 +1630,6 @@
       <c r="H20" t="n">
         <v>25</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>后台口偶遇</t>
@@ -1689,8 +1640,6 @@
           <t>散场后在后台口等到片刻，拍到上车前挥手。</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
         <v>480</v>
       </c>
@@ -1737,7 +1686,6 @@
       <c r="H21" t="n">
         <v>10</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>工作人员通道</t>
@@ -1748,8 +1696,6 @@
           <t>工作人员通道边远远拍到一组，算意外收获。</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
         <v>720</v>
       </c>
@@ -1813,8 +1759,6 @@
           <t>新手引导预置帖，曝光秒结算。</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -1831,6 +1775,67 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3010</v>
+      </c>
+      <c r="B23" t="n">
+        <v>301</v>
+      </c>
+      <c r="C23" t="n">
+        <v>903</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>sign_tutorial_a</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>签售中签·前排repo</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>教程签售必中A档嫂子帖。</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>240</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>0</v>
       </c>
     </row>
